--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:01</t>
+    <t xml:space="preserve">2026-09-24 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -662,13 +662,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.54</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="8">
@@ -685,13 +685,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="9">
@@ -708,13 +708,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>0.24</v>
-      </c>
       <c r="G9" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -731,13 +731,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.63</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="11">
@@ -754,13 +754,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.61</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="12">
@@ -777,13 +777,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="13">
@@ -800,13 +800,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         <v>-0.37</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.19</v>
@@ -849,10 +849,10 @@
         <v>-0.11</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="16">
@@ -869,13 +869,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.17</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="18">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
@@ -957,13 +957,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="21">
@@ -980,13 +980,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>-0.04</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="22">
@@ -1101,10 +1101,10 @@
         <v>0.24</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="28">
@@ -1121,13 +1121,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="30">
@@ -1167,13 +1167,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="31">
@@ -1190,13 +1190,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="32">
@@ -1213,13 +1213,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="33">
@@ -1242,7 +1242,7 @@
         <v>0.25</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="34">
@@ -1305,13 +1305,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -1328,13 +1328,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>-0.18</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="38">
@@ -1370,13 +1370,13 @@
         <v>30</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="40">
@@ -1393,10 +1393,10 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>-0.12</v>
@@ -1416,13 +1416,13 @@
         <v>30</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="42">
@@ -1806,13 +1806,13 @@
         <v>30</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="60">
@@ -1829,13 +1829,13 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="61">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:52</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
